--- a/outputs/45707.xlsx
+++ b/outputs/45707.xlsx
@@ -344,7 +344,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f aca="false">IF(DAY(A2+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A2),MONTH(A2),1),A:A,"&lt;"&amp;DATE(YEAR(A2),MONTH(A2)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A2+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A2)*(YEAR(A$2:A$69)=YEAR(A2)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -354,7 +354,7 @@
         <v>36527</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f aca="false">IF(DAY(A3+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A3),MONTH(A3),1),A:A,"&lt;"&amp;DATE(YEAR(A3),MONTH(A3)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A3+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A3)*(YEAR(A$2:A$69)=YEAR(A3)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -364,7 +364,7 @@
         <v>36528</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f aca="false">IF(DAY(A4+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A4),MONTH(A4),1),A:A,"&lt;"&amp;DATE(YEAR(A4),MONTH(A4)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A4+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A4)*(YEAR(A$2:A$69)=YEAR(A4)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -374,7 +374,7 @@
         <v>36529</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f aca="false">IF(DAY(A5+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A5),MONTH(A5),1),A:A,"&lt;"&amp;DATE(YEAR(A5),MONTH(A5)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A5+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A5)*(YEAR(A$2:A$69)=YEAR(A5)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -384,7 +384,7 @@
         <v>36530</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f aca="false">IF(DAY(A6+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A6),MONTH(A6),1),A:A,"&lt;"&amp;DATE(YEAR(A6),MONTH(A6)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A6+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A6)*(YEAR(A$2:A$69)=YEAR(A6)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -394,7 +394,7 @@
         <v>36531</v>
       </c>
       <c r="D7" s="1" t="str">
-        <f aca="false">IF(DAY(A7+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A7),MONTH(A7),1),A:A,"&lt;"&amp;DATE(YEAR(A7),MONTH(A7)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A7+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A7)*(YEAR(A$2:A$69)=YEAR(A7)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -404,7 +404,7 @@
         <v>36532</v>
       </c>
       <c r="D8" s="1" t="str">
-        <f aca="false">IF(DAY(A8+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A8),MONTH(A8),1),A:A,"&lt;"&amp;DATE(YEAR(A8),MONTH(A8)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A8+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A8)*(YEAR(A$2:A$69)=YEAR(A8)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="str">
-        <f aca="false">IF(DAY(A9+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A9),MONTH(A9),1),A:A,"&lt;"&amp;DATE(YEAR(A9),MONTH(A9)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A9+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A9)*(YEAR(A$2:A$69)=YEAR(A9)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -427,7 +427,7 @@
         <v>36534</v>
       </c>
       <c r="D10" s="1" t="str">
-        <f aca="false">IF(DAY(A10+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A10),MONTH(A10),1),A:A,"&lt;"&amp;DATE(YEAR(A10),MONTH(A10)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A10+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A10)*(YEAR(A$2:A$69)=YEAR(A10)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -437,7 +437,7 @@
         <v>36535</v>
       </c>
       <c r="D11" s="1" t="str">
-        <f aca="false">IF(DAY(A11+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A11),MONTH(A11),1),A:A,"&lt;"&amp;DATE(YEAR(A11),MONTH(A11)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A11+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A11)*(YEAR(A$2:A$69)=YEAR(A11)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -447,7 +447,7 @@
         <v>36536</v>
       </c>
       <c r="D12" s="1" t="str">
-        <f aca="false">IF(DAY(A12+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A12),MONTH(A12),1),A:A,"&lt;"&amp;DATE(YEAR(A12),MONTH(A12)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A12+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A12)*(YEAR(A$2:A$69)=YEAR(A12)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -457,7 +457,7 @@
         <v>36537</v>
       </c>
       <c r="D13" s="1" t="str">
-        <f aca="false">IF(DAY(A13+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A13),MONTH(A13),1),A:A,"&lt;"&amp;DATE(YEAR(A13),MONTH(A13)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A13+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A13)*(YEAR(A$2:A$69)=YEAR(A13)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -467,7 +467,7 @@
         <v>36538</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f aca="false">IF(DAY(A14+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A14),MONTH(A14),1),A:A,"&lt;"&amp;DATE(YEAR(A14),MONTH(A14)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A14+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A14)*(YEAR(A$2:A$69)=YEAR(A14)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -480,7 +480,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="str">
-        <f aca="false">IF(DAY(A15+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A15),MONTH(A15),1),A:A,"&lt;"&amp;DATE(YEAR(A15),MONTH(A15)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A15+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A15)*(YEAR(A$2:A$69)=YEAR(A15)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -490,7 +490,7 @@
         <v>36540</v>
       </c>
       <c r="D16" s="1" t="str">
-        <f aca="false">IF(DAY(A16+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A16),MONTH(A16),1),A:A,"&lt;"&amp;DATE(YEAR(A16),MONTH(A16)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A16+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A16)*(YEAR(A$2:A$69)=YEAR(A16)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         <v>36541</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f aca="false">IF(DAY(A17+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A17),MONTH(A17),1),A:A,"&lt;"&amp;DATE(YEAR(A17),MONTH(A17)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A17+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A17)*(YEAR(A$2:A$69)=YEAR(A17)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -510,7 +510,7 @@
         <v>36542</v>
       </c>
       <c r="D18" s="1" t="str">
-        <f aca="false">IF(DAY(A18+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A18),MONTH(A18),1),A:A,"&lt;"&amp;DATE(YEAR(A18),MONTH(A18)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A18+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A18)*(YEAR(A$2:A$69)=YEAR(A18)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -520,7 +520,7 @@
         <v>36543</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f aca="false">IF(DAY(A19+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A19),MONTH(A19),1),A:A,"&lt;"&amp;DATE(YEAR(A19),MONTH(A19)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A19+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A19)*(YEAR(A$2:A$69)=YEAR(A19)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -533,7 +533,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="str">
-        <f aca="false">IF(DAY(A20+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A20),MONTH(A20),1),A:A,"&lt;"&amp;DATE(YEAR(A20),MONTH(A20)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A20+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A20)*(YEAR(A$2:A$69)=YEAR(A20)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -543,7 +543,7 @@
         <v>36545</v>
       </c>
       <c r="D21" s="1" t="str">
-        <f aca="false">IF(DAY(A21+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A21),MONTH(A21),1),A:A,"&lt;"&amp;DATE(YEAR(A21),MONTH(A21)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A21+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A21)*(YEAR(A$2:A$69)=YEAR(A21)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -553,7 +553,7 @@
         <v>36546</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f aca="false">IF(DAY(A22+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A22),MONTH(A22),1),A:A,"&lt;"&amp;DATE(YEAR(A22),MONTH(A22)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A22+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A22)*(YEAR(A$2:A$69)=YEAR(A22)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -563,7 +563,7 @@
         <v>36547</v>
       </c>
       <c r="D23" s="1" t="str">
-        <f aca="false">IF(DAY(A23+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A23),MONTH(A23),1),A:A,"&lt;"&amp;DATE(YEAR(A23),MONTH(A23)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A23+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A23)*(YEAR(A$2:A$69)=YEAR(A23)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -573,7 +573,7 @@
         <v>36548</v>
       </c>
       <c r="D24" s="1" t="str">
-        <f aca="false">IF(DAY(A24+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A24),MONTH(A24),1),A:A,"&lt;"&amp;DATE(YEAR(A24),MONTH(A24)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A24+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A24)*(YEAR(A$2:A$69)=YEAR(A24)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -583,7 +583,7 @@
         <v>36549</v>
       </c>
       <c r="D25" s="1" t="str">
-        <f aca="false">IF(DAY(A25+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A25),MONTH(A25),1),A:A,"&lt;"&amp;DATE(YEAR(A25),MONTH(A25)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A25+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A25)*(YEAR(A$2:A$69)=YEAR(A25)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="str">
-        <f aca="false">IF(DAY(A26+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A26),MONTH(A26),1),A:A,"&lt;"&amp;DATE(YEAR(A26),MONTH(A26)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A26+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A26)*(YEAR(A$2:A$69)=YEAR(A26)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         <v>36551</v>
       </c>
       <c r="D27" s="1" t="str">
-        <f aca="false">IF(DAY(A27+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A27),MONTH(A27),1),A:A,"&lt;"&amp;DATE(YEAR(A27),MONTH(A27)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A27+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A27)*(YEAR(A$2:A$69)=YEAR(A27)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -616,7 +616,7 @@
         <v>36552</v>
       </c>
       <c r="D28" s="1" t="str">
-        <f aca="false">IF(DAY(A28+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A28),MONTH(A28),1),A:A,"&lt;"&amp;DATE(YEAR(A28),MONTH(A28)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A28+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A28)*(YEAR(A$2:A$69)=YEAR(A28)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -626,7 +626,7 @@
         <v>36553</v>
       </c>
       <c r="D29" s="1" t="str">
-        <f aca="false">IF(DAY(A29+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A29),MONTH(A29),1),A:A,"&lt;"&amp;DATE(YEAR(A29),MONTH(A29)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A29+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A29)*(YEAR(A$2:A$69)=YEAR(A29)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -636,7 +636,7 @@
         <v>36554</v>
       </c>
       <c r="D30" s="1" t="str">
-        <f aca="false">IF(DAY(A30+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A30),MONTH(A30),1),A:A,"&lt;"&amp;DATE(YEAR(A30),MONTH(A30)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A30+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A30)*(YEAR(A$2:A$69)=YEAR(A30)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -646,7 +646,7 @@
         <v>36555</v>
       </c>
       <c r="D31" s="1" t="str">
-        <f aca="false">IF(DAY(A31+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A31),MONTH(A31),1),A:A,"&lt;"&amp;DATE(YEAR(A31),MONTH(A31)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A31+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A31)*(YEAR(A$2:A$69)=YEAR(A31)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -656,7 +656,7 @@
         <v>36556</v>
       </c>
       <c r="D32" s="2" t="n">
-        <f aca="false">IF(DAY(A32+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A32),MONTH(A32),1),A:A,"&lt;"&amp;DATE(YEAR(A32),MONTH(A32)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A32+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A32)*(YEAR(A$2:A$69)=YEAR(A32)))*(C$2:C$69=1)),"")</f>
         <v>5</v>
       </c>
     </row>
@@ -666,7 +666,7 @@
         <v>36557</v>
       </c>
       <c r="D33" s="1" t="str">
-        <f aca="false">IF(DAY(A33+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A33),MONTH(A33),1),A:A,"&lt;"&amp;DATE(YEAR(A33),MONTH(A33)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A33+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A33)*(YEAR(A$2:A$69)=YEAR(A33)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -676,7 +676,7 @@
         <v>36558</v>
       </c>
       <c r="D34" s="1" t="str">
-        <f aca="false">IF(DAY(A34+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A34),MONTH(A34),1),A:A,"&lt;"&amp;DATE(YEAR(A34),MONTH(A34)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A34+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A34)*(YEAR(A$2:A$69)=YEAR(A34)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="str">
-        <f aca="false">IF(DAY(A35+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A35),MONTH(A35),1),A:A,"&lt;"&amp;DATE(YEAR(A35),MONTH(A35)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A35+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A35)*(YEAR(A$2:A$69)=YEAR(A35)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>36560</v>
       </c>
       <c r="D36" s="1" t="str">
-        <f aca="false">IF(DAY(A36+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A36),MONTH(A36),1),A:A,"&lt;"&amp;DATE(YEAR(A36),MONTH(A36)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A36+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A36)*(YEAR(A$2:A$69)=YEAR(A36)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -709,7 +709,7 @@
         <v>36561</v>
       </c>
       <c r="D37" s="1" t="str">
-        <f aca="false">IF(DAY(A37+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A37),MONTH(A37),1),A:A,"&lt;"&amp;DATE(YEAR(A37),MONTH(A37)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A37+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A37)*(YEAR(A$2:A$69)=YEAR(A37)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -719,7 +719,7 @@
         <v>36562</v>
       </c>
       <c r="D38" s="1" t="str">
-        <f aca="false">IF(DAY(A38+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A38),MONTH(A38),1),A:A,"&lt;"&amp;DATE(YEAR(A38),MONTH(A38)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A38+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A38)*(YEAR(A$2:A$69)=YEAR(A38)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -729,7 +729,7 @@
         <v>36563</v>
       </c>
       <c r="D39" s="1" t="str">
-        <f aca="false">IF(DAY(A39+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A39),MONTH(A39),1),A:A,"&lt;"&amp;DATE(YEAR(A39),MONTH(A39)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A39+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A39)*(YEAR(A$2:A$69)=YEAR(A39)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -739,7 +739,7 @@
         <v>36564</v>
       </c>
       <c r="D40" s="1" t="str">
-        <f aca="false">IF(DAY(A40+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A40),MONTH(A40),1),A:A,"&lt;"&amp;DATE(YEAR(A40),MONTH(A40)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A40+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A40)*(YEAR(A$2:A$69)=YEAR(A40)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -752,7 +752,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="1" t="str">
-        <f aca="false">IF(DAY(A41+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A41),MONTH(A41),1),A:A,"&lt;"&amp;DATE(YEAR(A41),MONTH(A41)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A41+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A41)*(YEAR(A$2:A$69)=YEAR(A41)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -762,7 +762,7 @@
         <v>36566</v>
       </c>
       <c r="D42" s="1" t="str">
-        <f aca="false">IF(DAY(A42+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A42),MONTH(A42),1),A:A,"&lt;"&amp;DATE(YEAR(A42),MONTH(A42)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A42+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A42)*(YEAR(A$2:A$69)=YEAR(A42)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>36567</v>
       </c>
       <c r="D43" s="1" t="str">
-        <f aca="false">IF(DAY(A43+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A43),MONTH(A43),1),A:A,"&lt;"&amp;DATE(YEAR(A43),MONTH(A43)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A43+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A43)*(YEAR(A$2:A$69)=YEAR(A43)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         <v>36568</v>
       </c>
       <c r="D44" s="1" t="str">
-        <f aca="false">IF(DAY(A44+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A44),MONTH(A44),1),A:A,"&lt;"&amp;DATE(YEAR(A44),MONTH(A44)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A44+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A44)*(YEAR(A$2:A$69)=YEAR(A44)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -792,7 +792,7 @@
         <v>36569</v>
       </c>
       <c r="D45" s="1" t="str">
-        <f aca="false">IF(DAY(A45+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A45),MONTH(A45),1),A:A,"&lt;"&amp;DATE(YEAR(A45),MONTH(A45)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A45+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A45)*(YEAR(A$2:A$69)=YEAR(A45)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -802,7 +802,7 @@
         <v>36570</v>
       </c>
       <c r="D46" s="1" t="str">
-        <f aca="false">IF(DAY(A46+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A46),MONTH(A46),1),A:A,"&lt;"&amp;DATE(YEAR(A46),MONTH(A46)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A46+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A46)*(YEAR(A$2:A$69)=YEAR(A46)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -812,7 +812,7 @@
         <v>36571</v>
       </c>
       <c r="D47" s="1" t="str">
-        <f aca="false">IF(DAY(A47+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A47),MONTH(A47),1),A:A,"&lt;"&amp;DATE(YEAR(A47),MONTH(A47)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A47+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A47)*(YEAR(A$2:A$69)=YEAR(A47)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -822,7 +822,7 @@
         <v>36572</v>
       </c>
       <c r="D48" s="1" t="str">
-        <f aca="false">IF(DAY(A48+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A48),MONTH(A48),1),A:A,"&lt;"&amp;DATE(YEAR(A48),MONTH(A48)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A48+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A48)*(YEAR(A$2:A$69)=YEAR(A48)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>36573</v>
       </c>
       <c r="D49" s="1" t="str">
-        <f aca="false">IF(DAY(A49+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A49),MONTH(A49),1),A:A,"&lt;"&amp;DATE(YEAR(A49),MONTH(A49)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A49+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A49)*(YEAR(A$2:A$69)=YEAR(A49)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -842,7 +842,7 @@
         <v>36574</v>
       </c>
       <c r="D50" s="1" t="str">
-        <f aca="false">IF(DAY(A50+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A50),MONTH(A50),1),A:A,"&lt;"&amp;DATE(YEAR(A50),MONTH(A50)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A50+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A50)*(YEAR(A$2:A$69)=YEAR(A50)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -852,7 +852,7 @@
         <v>36575</v>
       </c>
       <c r="D51" s="1" t="str">
-        <f aca="false">IF(DAY(A51+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A51),MONTH(A51),1),A:A,"&lt;"&amp;DATE(YEAR(A51),MONTH(A51)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A51+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A51)*(YEAR(A$2:A$69)=YEAR(A51)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1" t="str">
-        <f aca="false">IF(DAY(A52+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A52),MONTH(A52),1),A:A,"&lt;"&amp;DATE(YEAR(A52),MONTH(A52)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A52+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A52)*(YEAR(A$2:A$69)=YEAR(A52)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -875,7 +875,7 @@
         <v>36577</v>
       </c>
       <c r="D53" s="1" t="str">
-        <f aca="false">IF(DAY(A53+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A53),MONTH(A53),1),A:A,"&lt;"&amp;DATE(YEAR(A53),MONTH(A53)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A53+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A53)*(YEAR(A$2:A$69)=YEAR(A53)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -885,7 +885,7 @@
         <v>36578</v>
       </c>
       <c r="D54" s="1" t="str">
-        <f aca="false">IF(DAY(A54+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A54),MONTH(A54),1),A:A,"&lt;"&amp;DATE(YEAR(A54),MONTH(A54)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A54+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A54)*(YEAR(A$2:A$69)=YEAR(A54)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -895,7 +895,7 @@
         <v>36579</v>
       </c>
       <c r="D55" s="1" t="str">
-        <f aca="false">IF(DAY(A55+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A55),MONTH(A55),1),A:A,"&lt;"&amp;DATE(YEAR(A55),MONTH(A55)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A55+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A55)*(YEAR(A$2:A$69)=YEAR(A55)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -905,7 +905,7 @@
         <v>36580</v>
       </c>
       <c r="D56" s="1" t="str">
-        <f aca="false">IF(DAY(A56+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A56),MONTH(A56),1),A:A,"&lt;"&amp;DATE(YEAR(A56),MONTH(A56)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A56+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A56)*(YEAR(A$2:A$69)=YEAR(A56)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -915,7 +915,7 @@
         <v>36581</v>
       </c>
       <c r="D57" s="1" t="str">
-        <f aca="false">IF(DAY(A57+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A57),MONTH(A57),1),A:A,"&lt;"&amp;DATE(YEAR(A57),MONTH(A57)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A57+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A57)*(YEAR(A$2:A$69)=YEAR(A57)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -925,7 +925,7 @@
         <v>36582</v>
       </c>
       <c r="D58" s="1" t="str">
-        <f aca="false">IF(DAY(A58+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A58),MONTH(A58),1),A:A,"&lt;"&amp;DATE(YEAR(A58),MONTH(A58)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A58+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A58)*(YEAR(A$2:A$69)=YEAR(A58)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>36583</v>
       </c>
       <c r="D59" s="1" t="str">
-        <f aca="false">IF(DAY(A59+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A59),MONTH(A59),1),A:A,"&lt;"&amp;DATE(YEAR(A59),MONTH(A59)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A59+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A59)*(YEAR(A$2:A$69)=YEAR(A59)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -945,7 +945,7 @@
         <v>36584</v>
       </c>
       <c r="D60" s="1" t="str">
-        <f aca="false">IF(DAY(A60+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A60),MONTH(A60),1),A:A,"&lt;"&amp;DATE(YEAR(A60),MONTH(A60)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A60+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A60)*(YEAR(A$2:A$69)=YEAR(A60)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -958,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="2" t="n">
-        <f aca="false">IF(DAY(A61+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A61),MONTH(A61),1),A:A,"&lt;"&amp;DATE(YEAR(A61),MONTH(A61)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A61+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A61)*(YEAR(A$2:A$69)=YEAR(A61)))*(C$2:C$69=1)),"")</f>
         <v>4</v>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v>36586</v>
       </c>
       <c r="D62" s="1" t="str">
-        <f aca="false">IF(DAY(A62+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A62),MONTH(A62),1),A:A,"&lt;"&amp;DATE(YEAR(A62),MONTH(A62)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A62+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A62)*(YEAR(A$2:A$69)=YEAR(A62)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -978,7 +978,7 @@
         <v>36587</v>
       </c>
       <c r="D63" s="1" t="str">
-        <f aca="false">IF(DAY(A63+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A63),MONTH(A63),1),A:A,"&lt;"&amp;DATE(YEAR(A63),MONTH(A63)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A63+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A63)*(YEAR(A$2:A$69)=YEAR(A63)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -988,7 +988,7 @@
         <v>36588</v>
       </c>
       <c r="D64" s="1" t="str">
-        <f aca="false">IF(DAY(A64+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A64),MONTH(A64),1),A:A,"&lt;"&amp;DATE(YEAR(A64),MONTH(A64)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A64+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A64)*(YEAR(A$2:A$69)=YEAR(A64)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -998,7 +998,7 @@
         <v>36589</v>
       </c>
       <c r="D65" s="1" t="str">
-        <f aca="false">IF(DAY(A65+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A65),MONTH(A65),1),A:A,"&lt;"&amp;DATE(YEAR(A65),MONTH(A65)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A65+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A65)*(YEAR(A$2:A$69)=YEAR(A65)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         <v>36590</v>
       </c>
       <c r="D66" s="1" t="str">
-        <f aca="false">IF(DAY(A66+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A66),MONTH(A66),1),A:A,"&lt;"&amp;DATE(YEAR(A66),MONTH(A66)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A66+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A66)*(YEAR(A$2:A$69)=YEAR(A66)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         <v>36591</v>
       </c>
       <c r="D67" s="1" t="str">
-        <f aca="false">IF(DAY(A67+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A67),MONTH(A67),1),A:A,"&lt;"&amp;DATE(YEAR(A67),MONTH(A67)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A67+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A67)*(YEAR(A$2:A$69)=YEAR(A67)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
         <v>36592</v>
       </c>
       <c r="D68" s="1" t="str">
-        <f aca="false">IF(DAY(A68+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A68),MONTH(A68),1),A:A,"&lt;"&amp;DATE(YEAR(A68),MONTH(A68)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A68+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A68)*(YEAR(A$2:A$69)=YEAR(A68)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         <v>36593</v>
       </c>
       <c r="D69" s="1" t="str">
-        <f aca="false">IF(DAY(A69+1)=1,COUNTIFS(C:C,1,A:A,"&gt;="&amp;DATE(YEAR(A69),MONTH(A69),1),A:A,"&lt;"&amp;DATE(YEAR(A69),MONTH(A69)+1,1)),"")</f>
+        <f aca="false">IF(DAY(A69+1)=1,SUMPRODUCT((MONTH(A$2:A$69)=MONTH(A69)*(YEAR(A$2:A$69)=YEAR(A69)))*(C$2:C$69=1)),"")</f>
         <v/>
       </c>
     </row>
